--- a/DB/questions.xlsx
+++ b/DB/questions.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\git\FE-portfolio\DB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\java09\Desktop\trainingmemo\ポートフォリオ\FE-portfolio\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD16A54-1EF3-4328-829C-5E2513C728EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24481681-48C8-4280-9B31-21B87B7CA1A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="questions" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="292">
   <si>
     <t>external_key</t>
     <phoneticPr fontId="1"/>
@@ -190,20 +191,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t xml:space="preserve">次の一連の3アドレス命令で得られる結果xを表す式はどれか。ここで、3アドレス命令では、三つのオペランドを用いた命令
-c←a op b
-を
-op(a,b,c)
-と表記する。また、opは一つの演算子を表し、結果xを表す式における演算子は、×,÷,+,-の順に優先度が高いものとする。
-÷(c,d,w1)
-</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>まだできてないです</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1件のトランザクションについて80万ステップの命令実行を必要とするシステムがある。プロセッサの性能が200MIPSで、プロセッサの使用率が80%の時のトランザクションの処理能力(件/秒)はいくらか。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -213,6 +200,3055 @@
 1秒につき処理できる命令数を、トランザクション1件に必要な命令数で割れば、1秒で処理できるトランザクション数を求めることができる。プロセッサの使用率が80%であることに注意すると
 200×1,000,000(命令/秒)×0.8÷800000(命令/件)=200(件/秒)
 となる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の一連の3アドレス命令で得られる結果xを表す式はどれか。ここで、3アドレス命令では、三つのオペランドを用いた命令
+c←a op b
+を
+op(a, b, c)
+と表記する。また、opは一つの演算子を表し、結果xを表す式における演算子は、×,÷,+,-の順に優先度が高いものとする。
+÷(c, d, w1)
++(b, w1, w2)
+÷(e, f, w3)
+-(w3, g, w4)
+×(w2, w4, x)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>←を=として一連の命令を書き換えると
+w1 = c÷d
+w2 = b + w1
+w3 = e ÷ f
+w4 = w3 - g
+x = w2 × w4
+となる。
+以上から、w1,w2,w3,w4を用いずにxを表すと
+x = (b + w1) × (w3 - g) = (b + c ÷ d) × (e ÷ f - g)
+とわかる。</t>
+    <rPh sb="6" eb="8">
+      <t>イチレン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>メイレイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ1</t>
+  </si>
+  <si>
+    <t>プロセッサ</t>
+  </si>
+  <si>
+    <t>1GHzのクロックで動作するCPUがある。このCPUは、機械語の1命令を平均0.8クロックで実行できることがわかっている。_x000D_
+このCPUは1秒間に平均何万命令を実行できるか。</t>
+  </si>
+  <si>
+    <t>1GHzのクロックで動作するCPUでは1秒間に10の9乗回のクロックが動作する。
+1命令を平均0.8クロックで実行できるので、10の9乗を0.8で割れば答えが求まる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ2</t>
+  </si>
+  <si>
+    <t>外部割込みの原因となるものはどれか。</t>
+  </si>
+  <si>
+    <t>割り込みとは、入出力装置からの信号や演算結果などの要因により、実行中のプログラムを中断して割込み処理用のプログラムに実行を移すことである。
+割り込みは発生要因によって内部割込みと外部割込みに分類される。
+内部割込みは、ソフトウェアの動作が要因で発生する割り込みのことである。
+外部割込みは、州出力装置などCPU外部のハードウェアが要因で発生する割り込みである。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ3</t>
+  </si>
+  <si>
+    <t>割り込み処理の終了後に割込みによって中断された処理を割り込まれた場所から再開するために、割り込み発生時にプロセッサが保存するものはどれか。</t>
+  </si>
+  <si>
+    <t>割り込みとは、入出力装置からの信号や演算結果などの要因により、実行中のプログラムを中断して割込み処理用のプログラムに実行を移すことである。
+割り込み発生時にプロセッサのプログラムカウンタが元の処理のアドレスを記憶するので、割り込み処理の終了後に元の処理に戻れる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ4</t>
+  </si>
+  <si>
+    <t>メモリ</t>
+  </si>
+  <si>
+    <t>メモリのエラー検出及び訂正にECCを利用している。データバス幅2^nビットに対して冗長ビットがn+2ビット必要な時、128ビットのデータバス幅に必要な冗長ビットは何ビットか。</t>
+  </si>
+  <si>
+    <t>まずnを求める。2^n=128ビットより、n=7である。したがって必要な冗長ビットはn+2=9ビットである。
+ちなみに、ECCとは、メモリに記憶されたデータの誤りを検出し、訂正する機能である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ5</t>
+  </si>
+  <si>
+    <t>キャッシュメモリに関する記述のうち、適切なものはどれか。</t>
+  </si>
+  <si>
+    <t>CPUは、コンピュータの動作に必要なデータやプログラムを主記憶装置とやり取りするが、主記憶装置はCPUに比べて低速であり、両者の速度差を埋めるために高速なキャッシュメモリが間で一時的にデータを保管する。
+キャッシュメモリと主記憶が整合性をとるためには、キャッシュメモリに書き込んだ内容を主記憶に反映させなければならない。この書き込み方式には「ライトスルー方式」と「ライトバック方式」の2種類がある。
+ライトスルー方式では、キャッシュメモリへの書き込みを行うと同時に主記憶にも書き込む。
+ライトバック方式では、キャッシュメモリからデータが追い出される際に、そのデータを主記憶に書き込む。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ6</t>
+  </si>
+  <si>
+    <t>DRAMの説明として、適切なものはどれか。</t>
+  </si>
+  <si>
+    <t>DRAM(Dynamic Random Access Memory)は、コンデンサに電荷を蓄えることにより情報を記憶し、電源供給がなくなると情報記憶も失われる揮発性メモリである。データの保持のためにリフレッシュ操作が必要である。安価で容量が大きく、主記憶装置に用いられるメモリである。</t>
+  </si>
+  <si>
+    <t>DBQ7</t>
+  </si>
+  <si>
+    <t>応用数学</t>
+  </si>
+  <si>
+    <t>Random(10)は0から9の整数を一様に返す。したがってAとBがとりうる値はともに10通りであり、その組み合わせの総数は100通りとなる。
+そしてC=A-B=0となるとき、A=Bが成立する。A=Bがとりうる値は0から9の10通りなので、Cの値が0になる確率は10/100=1/10となる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ8</t>
+  </si>
+  <si>
+    <t>標準偏差に関する記述のうち、適切なものはどれか。</t>
+  </si>
+  <si>
+    <t>標準偏差とは、分散の平方根である。分散は、偏差（平均値と各データの差）を2乗したものの平均値をとることで求められる。標準偏差と分散は、データの散らばり具合の指標となる。</t>
+  </si>
+  <si>
+    <t>DBQ9</t>
+  </si>
+  <si>
+    <t>浮動小数点形式で表現された数値の演算結果における丸目誤差の説明はどれか。</t>
+  </si>
+  <si>
+    <t>丸め誤差とは、指定された有効桁数で演算結果を表すために、切り捨て、切り上げ、四捨五入などで発生する誤差のことである。</t>
+  </si>
+  <si>
+    <t>DBQ10</t>
+  </si>
+  <si>
+    <t>正規分布の説明として、適切なものはどれか。</t>
+  </si>
+  <si>
+    <t>DBQ11</t>
+  </si>
+  <si>
+    <t>情報・通信・計測・制御の理論</t>
+  </si>
+  <si>
+    <t>機械学習における教師あり学習の説明として、最も適切なものはどれか。</t>
+  </si>
+  <si>
+    <t>機械学習の教師あり学習とは、コンピューターにデータとそれに対する正解を与えて、未知のデータに対しても正解を推論できるように学習させることである。</t>
+  </si>
+  <si>
+    <t>DBQ12</t>
+  </si>
+  <si>
+    <t>AIにおける機械学習の説明として、最も適切なものはどれか。</t>
+  </si>
+  <si>
+    <t>AIによる機械学習とは、コンピュータが大量のデータを用いて学習し、分類や予測を行えるようにする技術である。</t>
+  </si>
+  <si>
+    <t>DBQ13</t>
+  </si>
+  <si>
+    <t>AIにおけるディープラーニングの特徴はどれか。</t>
+  </si>
+  <si>
+    <t>ディープラーニングとは機械学習の手法の一つである。ディープラーニングの特徴は、人間の神経回路を模倣したシステムであるニューラルネットワークを多層にして用いていることである。</t>
+  </si>
+  <si>
+    <t>DBQ14</t>
+  </si>
+  <si>
+    <t>16進数の小数0.248を10進数の分数で表したものはどれか。</t>
+  </si>
+  <si>
+    <t>十進数の数xをn進数に直すには、x = n^0 × A + n^1 × B + n^2 × C...のように分解し、CBAとすれば良い。1未満の十進数の数をn進数に直すには、n^-1 × A + n^-2 × B + n^-3 × C...のように分解し、0.ABC...とする。</t>
+  </si>
+  <si>
+    <t>DBQ15</t>
+  </si>
+  <si>
+    <t>8ビットの値の全ビットを反転する操作はどれか。</t>
+  </si>
+  <si>
+    <t>「ビットを反転する」とは、ビット列のうちの0を1に、1を0にする操作である。このためには排他的論理和を用いる。被演算ビット0と1の排他的論理和は1となり、被演算ビット1と1の排他的論理和は0になる。
+よって、反転したいビット列と同じビット数の値「1111 1111」の排他的論理和をとれば、前ビットを反転できる。
+2進数「1111 1111」は16進数で表すと「FF」なので、これとの排他的論理和を取れば良いことがわかる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ16</t>
+  </si>
+  <si>
+    <t>最上位をパリティビットとする8ビット符号において、パリティビット以外の下位7ビットを得るためのビット演算はどれか。</t>
+  </si>
+  <si>
+    <t>特定位置のビットを取り出すためには、論理積を用いる。被演算ビット0と1の論理積は0となり、被演算ビット1と1の論理積は1になる。これを利用して、取り出したい位置は1、それ以外の位置は0にしたビット列を作り、論理積をとれば良い。
+本文で取り出したいのは下位７ビットなので、最上位ビットを0、それ以外を1としたビット列「0111 1111」と元の８ビット符号の論理積をとれば良い。
+2進数「0111 1111」は16進数で表すと「7F」なのでこれとの論理積をとれば良いことがわかる。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ17</t>
+  </si>
+  <si>
+    <t>10進数の演算式 7÷32 の結果を2進数で表したものはどれか。</t>
+  </si>
+  <si>
+    <t>DBQ18</t>
+  </si>
+  <si>
+    <t>ある整数値を、負数を2の補数で表現する2進表記で表すと最下位2ビットは"11"であった。10進表記法の下で、その整数値を4で割った時のあまりに関する記述として、適切なものどれか。ここで、除算の商は、絶対値の小数点以下を切り捨てるものとする。</t>
+  </si>
+  <si>
+    <t>補数とはコンピュータの中で負の数を表す方法である。正の数は先頭のビットが0になり、負の数は先頭のビットが1になる。ある数に対する2の補数は、その数の全ビットを反転して、最後に1を足すことで求められる。本文では、「ある整数値」が正の場合と負の場合とであまりの数が異なる可能性を考慮し、この二通りで場合分けする必要がある。
+【正の場合】
+3桁目より大きい桁は全て4で割り切れるので、下二桁のみを考えれば良い。下二桁は「11」であるので、10進数に直すと「3」である。よって、正の数だった場合の余りは3である。
+【負の数】
+正の数の時と同様に、下二桁についてのみ考えれば良い。2の補数の2の補数をとることによって元の数を得られるので、下二桁は「01」となり、10進数に直すと「−1」である。よって、負の数だった場合の余りは-1である。
+以上より、最下位2ビットが11である整数値を4で割ったら、その数が正なら余りは3、負なら余りは-1である。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ19</t>
+  </si>
+  <si>
+    <t>数値を2進数で表すレジスタがある。このレジスタに格納されている正の整数xを10倍する操作はどれか。ここで、桁溢れは起こらないものとする。</t>
+  </si>
+  <si>
+    <t>xをnビット左にシフトするとx×2^n、nビット右にシフトするとx×2^-nとなる。
+これをもとに、xを10倍する操作を選べばよい。</t>
+    <rPh sb="6" eb="7">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミギ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DBQ20</t>
+  </si>
+  <si>
+    <t>次に示す手順は、列中の少なくとも一つは1であるビット列が与えられたとき、最も右にある1を残し、他のビット全てを0にするアルゴリズムである。例えば、00101000が与えられたとき、00001000が求まる。aに入る論理演算はどれか。
+手順1  与えられたビット列Aを符号なしの２進数とみなし、Aから1を引き、結果をBとする。
+手順2  AとBの排他的論理和を求め、結果をCとする。
+AとCの(a)を求め、結果をAとする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題文に与えられたビット列00101000を手順通りに処理し、結果として00001000が求まる論理演算を選ぶ。</t>
+  </si>
+  <si>
+    <t>DBQ21</t>
+  </si>
+  <si>
+    <t>0以外の数値を浮動小数点表示で表現する場合、仮数部の最上位桁が0以外になるように、桁合わせする操作はどれか。ここで、仮数部の表現方法は、絶対値表現とする。</t>
+  </si>
+  <si>
+    <t>仮数部とは、浮動小数点数のうちの有効数字を構成する部分である。</t>
+  </si>
+  <si>
+    <t>question_key</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>choice_order</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>choice_text</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>is_correct</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>((X NAND Y) NAND X) NAND Y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(X NAND X) NAND (Y NAND Y)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(X NAND Y) NAND (X NAND Y)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X NAND (Y NAND (X NAND Y))</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01010000</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01010001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01010010</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01010011</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>打切り誤差</t>
+    <rPh sb="0" eb="2">
+      <t>ウチキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桁落ち誤差</t>
+    <rPh sb="0" eb="1">
+      <t>ケタ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゴサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報落ち</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絶対誤差</t>
+    <rPh sb="0" eb="2">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゴサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>|α|が1に比べて非常に小さい</t>
+  </si>
+  <si>
+    <t>|α|がnに比べて非常に大きい</t>
+  </si>
+  <si>
+    <t>|α÷n|が1より大きい</t>
+  </si>
+  <si>
+    <t>|n×α|が1より大きい</t>
+  </si>
+  <si>
+    <t>f(a)=y</t>
+  </si>
+  <si>
+    <t>f(y)=0</t>
+  </si>
+  <si>
+    <t>f(y)=a</t>
+  </si>
+  <si>
+    <t>f(y)=y</t>
+  </si>
+  <si>
+    <t>アナログからディジタルへの変換では誤差が発生しない。</t>
+    <rPh sb="13" eb="15">
+      <t>ヘンカン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゴサ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>演算結果が部品精度、温度変化及び外来雑音の影響を受けにくい。</t>
+    <rPh sb="0" eb="2">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブヒン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>オンド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ガイライ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ザツオン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値演算において丸め誤差が発生することはない。</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>マル</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゴサ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電圧が変化してから演算結果を得るまでの遅延時間が発生しない。</t>
+    <rPh sb="0" eb="2">
+      <t>デンアツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チエン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b+c÷d×e÷f-g</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b+c÷d×(e÷f-g)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(b+c÷d)×e÷f-g</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(b+c÷d)×(e÷f-g)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゼロによる除算命令の実行</t>
+  </si>
+  <si>
+    <t>存在しない命令コードの実行</t>
+  </si>
+  <si>
+    <t>タイマによる時間経過の通知</t>
+  </si>
+  <si>
+    <t>ページフォールトの発生</t>
+  </si>
+  <si>
+    <t>インデックスレジスタ</t>
+  </si>
+  <si>
+    <t>データレジスタ</t>
+  </si>
+  <si>
+    <t>プログラムカウンタ</t>
+  </si>
+  <si>
+    <t>命令レジスタ</t>
+  </si>
+  <si>
+    <t>キャッシュメモリにヒットしない場合に割込みが生じ、プログラムによって主記憶からキャッシュメモリにデータが転送される。</t>
+  </si>
+  <si>
+    <t>キャッシュメモリは、実記憶と仮想記憶のメモリ容量の差を埋めるために採用される。</t>
+  </si>
+  <si>
+    <t>データ書き込み命令を実行したときに、キャッシュメモリと主記憶の両方を書き換える方式と、キャッシュメモリだけを書き換えておき、主記憶の書き換えはキャッシュメモリから当該データが追い出されるときに行う方式とがある。</t>
+  </si>
+  <si>
+    <t>半導体メモリのアクセス速度の向上が著しいので、キャッシュメモリの必要性は減っている。</t>
+  </si>
+  <si>
+    <t>1バイト単位でデータの消去及び書き込みが可能な不揮発性のメモリであり、電源遮断時もデータ保持が必要な用途に用いられる</t>
+  </si>
+  <si>
+    <t>不揮発性のメモリでNAND型またはNOR型があり、SSDに用いられる。</t>
+  </si>
+  <si>
+    <t>メモリセルはフリップフロップで構成され、キャッシュメモリに用いられる。</t>
+  </si>
+  <si>
+    <t>リフレッシュ動作が必要なメモリであり、PCの主記憶として用いられる。</t>
+  </si>
+  <si>
+    <t>1/100</t>
+  </si>
+  <si>
+    <t>すべてのデータに定数aを加えたものの標準偏差は、元の標準偏差にaを加えたものになる。</t>
+  </si>
+  <si>
+    <t>すべてのデータに定数aを加えたものの標準偏差は、元の標準偏差のa倍になる。</t>
+  </si>
+  <si>
+    <t>すべてのデータを2倍したものの標準偏差は、元の標準偏差の1/2倍になる。</t>
+  </si>
+  <si>
+    <t>すべてのデータを2倍したものの標準偏差は、元の標準偏差の2倍になる。</t>
+  </si>
+  <si>
+    <t>演算結果がコンピュータの扱える最大値を超えることによって生じる誤差である。</t>
+  </si>
+  <si>
+    <t>数表現の桁数に限度があるので、最下位桁より小さい部分について四捨五入や切り上げ、切り捨てを行うことによって生じる誤差である。</t>
+  </si>
+  <si>
+    <t>乗除算において、指数部が小さいほうの数値の仮数部の下位部分が失われることによって生じる誤差である。</t>
+  </si>
+  <si>
+    <t>絶対値がほぼ等しい数値の加減算において、上位の有効数字が失われることによって生じる誤差である。</t>
+  </si>
+  <si>
+    <t>故障確率に用いられ、バスタブのような形状をした連続確率分布のこと。</t>
+  </si>
+  <si>
+    <t>すべての事象の起こる確率が等しい現象を表す確率分布のこと。</t>
+  </si>
+  <si>
+    <t>平均値を中心とする左右対称で釣鐘状の連続確率分布のこと。</t>
+  </si>
+  <si>
+    <t>離散的に発生し、発生確率は一定である離散確率分布のこと。</t>
+  </si>
+  <si>
+    <t>個々の行動に対しての良しあしを得点として与えることによって、得点が最も多く得られるような方策を学習する。</t>
+  </si>
+  <si>
+    <t>コンピュータ利用者の挙動データを蓄積し、挙動データの出現頻度に従って次の挙動を推論する。</t>
+  </si>
+  <si>
+    <t>正解のデータを提示したり、データが誤りであることを指摘したりすることによって、未知のデータに対して正誤を得ることを助ける。</t>
+  </si>
+  <si>
+    <t>正解のデータを提示せずに、統計的性質や、ある種の条件によって入力パターンを判定したり、クラスタリングしたりする。</t>
+  </si>
+  <si>
+    <t>記憶したデータから特定のパターンを見つけ出すなどの、人が自然に行っている学習能力をコンピュータに持たせるための技術。</t>
+  </si>
+  <si>
+    <t>コンピュータ、機械などを使って、生命現象や進化のプロセスを再現するための技術。</t>
+  </si>
+  <si>
+    <t>特定の分野の専門知識をコンピュータに入力し、入力された知識を用いてコンピュータが推論する技術。</t>
+  </si>
+  <si>
+    <t>人が双方向学習を行うために、Webシステムなどの情報技術を用いて、教材や学習管理能力をコンピュータに持たせるための技術。</t>
+  </si>
+  <si>
+    <t>"AならばBである"というルールを人間があらかじめ設定して、新しい知識を論理式で表現したルールに基づく推論の結果として、解を求めるものである。</t>
+  </si>
+  <si>
+    <t>厳密な解でなくてもなるべく正解に近い解を得るようにする方法であり、特定分野に特化せずに、広範囲で汎用的な問題解決ができるようにするものである。</t>
+  </si>
+  <si>
+    <t>人間の神経回路を模倣して、認識などの知能を実現する方法であり、ニューラルネットワークを用いて、人間と同じような認識ができるようにするものである。</t>
+  </si>
+  <si>
+    <t>判断ルールを作成できる医療診断などの分野に限定されるが、症状から特定の病気に絞り込むといった、確率的に高い判断ができる。</t>
+  </si>
+  <si>
+    <t>31/32</t>
+  </si>
+  <si>
+    <t>31/125</t>
+  </si>
+  <si>
+    <t>31/512</t>
+  </si>
+  <si>
+    <t>73/512</t>
+  </si>
+  <si>
+    <t>16進表記 00 のビット列と排他的論理和をとる。</t>
+  </si>
+  <si>
+    <t>16進表記 00 のビット列と論理和をとる。</t>
+  </si>
+  <si>
+    <t>16進表記 FF のビット列と排他的論理和をとる。</t>
+  </si>
+  <si>
+    <t>16進表記 FF のビット列と論理和をとる。</t>
+  </si>
+  <si>
+    <t>16進数 0F とのANDをとる。</t>
+  </si>
+  <si>
+    <t>16進数 0f とのORをとる。</t>
+  </si>
+  <si>
+    <t>16進数 7F とのANDをとる。</t>
+  </si>
+  <si>
+    <t>16進数 FF とのXORをとる。</t>
+  </si>
+  <si>
+    <t>その整数値が正ならば3</t>
+  </si>
+  <si>
+    <t>その整数値が負ならば-3</t>
+  </si>
+  <si>
+    <t>その整数値が負ならば3</t>
+  </si>
+  <si>
+    <t>その整数値の正負に関わらず0</t>
+  </si>
+  <si>
+    <t>xを2ビット左にシフトした値にxを加算し、更に1ビット左にシフトする。</t>
+  </si>
+  <si>
+    <t>xを2ビット左にシフトした値にxを加算し、更に2ビット左にシフトする。</t>
+  </si>
+  <si>
+    <t>xを3ビット左にシフトした値と、xを2ビット左にシフトした値を加算する。</t>
+  </si>
+  <si>
+    <t>xを3ビット左にシフトした値にxを加算し、更に1ビット左にシフトする。</t>
+  </si>
+  <si>
+    <t>排他的論理和</t>
+  </si>
+  <si>
+    <t>否定論理和</t>
+  </si>
+  <si>
+    <t>論理積</t>
+  </si>
+  <si>
+    <t>論理和</t>
+  </si>
+  <si>
+    <t>切り上げ</t>
+  </si>
+  <si>
+    <t>切り捨て</t>
+  </si>
+  <si>
+    <t>桁上げ</t>
+  </si>
+  <si>
+    <t>正規化</t>
+  </si>
+  <si>
+    <t>Q12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>離散数学</t>
+    <rPh sb="0" eb="2">
+      <t>リサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スウガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンピュータで連立一次方程式の解を求めるのに、式に含まれる未知数の個数の3乗に比例する計算時間がかかるとする。あるコンピュータで100元連立一次方程式の解を求めるのに2秒かかったとすると、その4倍の演算速度を持つコンピュータで1000元連立一次方程式の解を求めるときの計算時間は何秒か。</t>
+    <rPh sb="7" eb="9">
+      <t>レンリツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチジ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ホウテイシキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>シキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>ミチスウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ヒレイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>レンリツ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>イチジ</t>
+    </rPh>
+    <rPh sb="72" eb="75">
+      <t>ホウテイシキ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>ゲン</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>レンリツ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>イチジ</t>
+    </rPh>
+    <rPh sb="122" eb="125">
+      <t>ホウテイシキ</t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="136" eb="138">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>ナンビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未知数の個数が10倍になったため、コンピュータの演算速度が同じであれば、計算時間は2×10^3=2000[秒]になる。
+今回は、元のコンピュータの4倍の演算速度を持つので、2000÷4=500[秒]となる。</t>
+    <rPh sb="0" eb="3">
+      <t>ミチスウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コスウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q12</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q13</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力待ちの印刷要求を、同一機種の3台のプリンタA~CのうちAから順に空いているプリンタに割り当てる（Cの次は再びAに戻る）システムがある。印刷要求の印刷時間が出力待ちの順に、5, 12, 4, 3, 10, 4(分)である場合、印刷に要した時間が長い順にプリンタを並べたものはどれか。ここで、初期状態ではプリンタは全て空いているものとする。</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ドウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キシュ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>フタタ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="81" eb="82">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="117" eb="118">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="125" eb="126">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="132" eb="133">
+      <t>ナラ</t>
+    </rPh>
+    <rPh sb="146" eb="148">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="157" eb="158">
+      <t>スベ</t>
+    </rPh>
+    <rPh sb="159" eb="160">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>問題文に従い、印刷要求をA, B, Cに割り当て、それぞれの合計処理時間を計算すればよい。
+①5分 : すべてのプリンターが空いているのでAに割り当てる
+②12分 : B. Cが空いているのでBに割り当てる
+③4分 : Cのみ空いているのでCに割り当てる
+④3分 : ③まででCが一番先に空くので、Cに割り当てる
+⑤10分 : Aのみ空くので、Aに割り当てる
+⑥4分 : Cのみ空くので、Cに割り当てる
+よって、各プリンターの印刷時間は次のようになる。
+A : 5+10=15
+B : 12
+C : 4+3+4=11</t>
+    <rPh sb="0" eb="3">
+      <t>モンダイブン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ケイサン</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="98" eb="99">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="122" eb="123">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="124" eb="125">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="130" eb="131">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>イチバン</t>
+    </rPh>
+    <rPh sb="142" eb="143">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="144" eb="145">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="151" eb="152">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="167" eb="168">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="174" eb="175">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="176" eb="177">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="182" eb="183">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="196" eb="197">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="198" eb="199">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="206" eb="207">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="213" eb="215">
+      <t>インサツ</t>
+    </rPh>
+    <rPh sb="215" eb="217">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="218" eb="219">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q13</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A, B, C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B, A, C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B, C, A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C, B, A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Random(n)は、0以上n未満の整数を一様な確率で返す関数である。整数型の変数A、B及びCに対して次の一連の手続きを実行したとき、Cの値が0になる確率はどれか。
+A = Random(10)
+B = Random(10)
+C = A - B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解説が難しい</t>
+    <rPh sb="0" eb="2">
+      <t>カイセツ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ムズカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報・通信・計測・制御の理論</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q21</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q23</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>送信側では、ビット列をある生成多項式で割った余りをそのビット列に付加して送信し、受信側では、受信したビット列が同じ生成多項式で割り切れるか否かで誤りの発生を判断する誤り検査方式はどれか。</t>
+    <rPh sb="0" eb="2">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>タコウシキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="59" eb="62">
+      <t>タコウシキ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>イナ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ケンサ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>送信側がビット列を生成多項式で割った余りをそのビット列に付加して送信し、受信側は受信したビット列（元のビット列+余り）が同じ生成多項式で割り切れるか否かで誤りの発生を判断する検査方式は、CRC(Cyclic Redundancy Check:巡回冗長検査)方式である。</t>
+    <rPh sb="0" eb="2">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>タコウシキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ソウシン</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジュシン</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>アマ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>タコウシキ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>イナ</t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>ハンダン</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ケンサ</t>
+    </rPh>
+    <rPh sb="89" eb="91">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>ジュンカイ</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>ジョウチョウ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ケンサ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CRC方式</t>
+    <rPh sb="3" eb="5">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>垂直パリティチェック方式</t>
+    <rPh sb="0" eb="2">
+      <t>スイチョク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水平パリティチェック方式</t>
+    <rPh sb="0" eb="2">
+      <t>スイヘイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハミング符号方式</t>
+    <rPh sb="4" eb="6">
+      <t>フゴウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィードバック制御の説明として、適切なものはどれか。</t>
+    <rPh sb="7" eb="9">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フィードバック制御とは、現在の状態を定期的に測定し、そのs句低地の目標値に近づけるように操作を自動的に制御する方式である。エアコンなどに使われる。</t>
+    <rPh sb="7" eb="9">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>テイキテキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>テイチ</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>モクヒョウチ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="47" eb="50">
+      <t>ジドウテキ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あらかじめ決められた順序で制御を行う</t>
+    <rPh sb="5" eb="6">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジュンジョ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外乱の影響が出力に現れる前に制御を行う</t>
+    <rPh sb="0" eb="2">
+      <t>ガイラン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力結果と目標値とを比較して、一致するように制御を行う</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>モクヒョウチ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力結果を使用せず制御を行う</t>
+    <rPh sb="0" eb="2">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIにおけるディープーラニングに関する記述として、最も適切なものはどれか。</t>
+    <rPh sb="16" eb="17">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディープラーニング（Deep Learning:深層学習）とは機械学習の手法の一つである。ディープラーニングの特徴は、人間の神経回路を模倣したシステムである、ニューラルネットワークを多層にして用いている点である。</t>
+    <rPh sb="24" eb="26">
+      <t>シンソウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>シンケイ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>カイロ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>モホウ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>タソウ</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="101" eb="102">
+      <t>テン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あるデータから結果を求める処理を、人間の脳神経回路のように多層の処理を重ねることによって、複雑な判断をできるようにする。</t>
+    <rPh sb="7" eb="9">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニンゲン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シンケイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カイロ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>タソウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>カサ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>フクザツ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ハンダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大量のデータからまだ知られていない新たな規則や仮説を発見するために、総低地から大きく外れている例外事項を取り除きながら分析を繰り返す手法である。</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キソク</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>カセツ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ハッケン</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>テイチ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ハズ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジコウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="66" eb="68">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>多様なデータや大量のデータに対して、三段論法、統計的手法やパターン認識手法を組み合わせることによって、高度なデータ分析を行う手法である。</t>
+    <rPh sb="0" eb="2">
+      <t>タヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>タイリョウ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サンダン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ロンポウ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>トウケイテキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ニンシキ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>コウド</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知識がルールに従って表現されており、演繹手法を利用した推論によって有意な結論を導く手法である。</t>
+    <rPh sb="0" eb="2">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>エンエキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>スイロン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ユウイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ケツロン</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>ミチビ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>シュホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大規模言語モデルを用いた自然言語処理において、事前学習済みのモデルに対して行う、ファインチューニングに関する記述として、最も適切なものはどれか。</t>
+    <rPh sb="0" eb="3">
+      <t>ダイキボ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シゼン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゲンゴ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>テキセツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファインチューニングは、事前学習で一般的な処理の精度を高めたAIモデルを、追加の学習データによって特定の分野や目的に合わせて調整することを指す。</t>
+    <rPh sb="12" eb="14">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>イッパンテキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ブンヤ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強化学習を行い、最適な結果が得られるようにする。</t>
+    <rPh sb="0" eb="2">
+      <t>キョウカ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サイテキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事前学習と同じデータを繰り返し用いて学習を行い、モデルの精度を高めるようにする。</t>
+    <rPh sb="0" eb="2">
+      <t>ジゼン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大量のテキストデータを用いて学習を行い、モデルの精度を高めるようにする。</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>タカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>特定のデータを用いて追加で学習を行い、目的とするタスクに適用できるようにする。</t>
+    <rPh sb="0" eb="2">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AIにおけるディープーラニングに最も関連が深いものはどれか。</t>
+    <rPh sb="16" eb="17">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ディープラーニングは、機械学習の一種で、脳の神経回路を模した「ニューラルネットワーク」を多層に構成して学習を行う手法である。
+入力層・中間層・出力層から成るネットワークに大量のデータを与えることで、コンピュータが特徴やパターンを自動的に学習し、分類や予測などの処理が可能になる。</t>
+    <rPh sb="11" eb="13">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>イッシュ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シンケイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カイロ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>タソウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>シュホウ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>チュウカン</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ソウ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>タイリョウ</t>
+    </rPh>
+    <rPh sb="92" eb="93">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="114" eb="117">
+      <t>ジドウテキ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ブンルイ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ヨソク</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ある特定の分野に特化した知識を基に、ルールベースの推論を行うことによって、専門家と同じレベルの問題解決を行う。</t>
+    <rPh sb="2" eb="4">
+      <t>トクテイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ブンヤ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トッカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>チシキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>モト</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>スイロン</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>センモンカ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カイケツ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>試行錯誤しながら条件を満たす会に到達する方法であり、場合分けを行い深さ優先で探索し、解が見つからなければひとつ前の場合分けの状態に後戻りする。</t>
+    <rPh sb="0" eb="2">
+      <t>シコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウタツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ユウセン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>タンサク</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>アトモド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神経回路網を模倣した方法であり、多層に配置された素子とそれらを結ぶ信号線で構成されたモデルにおいて、信号線に付随するパラメタを調整することによって入力に対して適切な解が出力される。</t>
+    <rPh sb="0" eb="2">
+      <t>シンケイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>カイロモウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>タソウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ソシ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ムス</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シンゴウ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>シンゴウ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>フズイ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="73" eb="75">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="82" eb="83">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>生物の進化を模倣した方法であり、与えられた問題の解の候補を記号列で表現して、それらを遺伝子に見立てて突然変異、後輩、淘汰を繰り返して逐次的により良い解に近づける。</t>
+    <rPh sb="0" eb="2">
+      <t>セイブツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンカ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モンダイ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウホ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>イデンシ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ミタ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>トツゼン</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ヘンイ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>コウハイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>トウタ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="66" eb="69">
+      <t>チクジテキ</t>
+    </rPh>
+    <rPh sb="72" eb="73">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="76" eb="77">
+      <t>チカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>メモリの誤り検出及び訂正を行う方式のうち、2ビットの誤り検知機能と、1ビットの誤り訂正機能を持つのはどれか。</t>
+    <rPh sb="4" eb="5">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ケンチ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>選択肢のうち、奇数パリティ、水平パリティ、チェックサムは誤り検出機能のみを持つ。ハミング記号は誤り検出機能と誤り訂正機能の2つの機能を持つ。</t>
+    <rPh sb="0" eb="3">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キスウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>スイヘイ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>キゴウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ケンシュツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>アヤマ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>テイセイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>奇数パリティ</t>
+    <rPh sb="0" eb="2">
+      <t>キスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水平パリティ</t>
+    <rPh sb="0" eb="2">
+      <t>スイヘイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チェックサム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ABC+99</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ABC99＊</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ABCDEF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UNIXにおける正規表現[A-Z] + [0-9]＊が表現する文字列の集合の要素となるものはどれか。ここで、正規表現は次の規則の従う。
+[A-Z]は、大文字の英字1文字を表す。
+[0-9]は、数字1文字を表す。
++は、直前の正規表現の1回以上の繰り返しであることを表す。
+＊は、直前の正規表現の0回以上の繰り返しであることを表す。</t>
+    <rPh sb="8" eb="10">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="31" eb="34">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>シュウゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>キソク</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="76" eb="79">
+      <t>オオモジ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>エイジ</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="86" eb="87">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>スウジ</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="103" eb="104">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="119" eb="122">
+      <t>カイイジョウ</t>
+    </rPh>
+    <rPh sb="123" eb="124">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="125" eb="126">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="140" eb="142">
+      <t>チョクゼン</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="149" eb="152">
+      <t>カイイジョウ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="155" eb="156">
+      <t>カエ</t>
+    </rPh>
+    <rPh sb="163" eb="164">
+      <t>アラワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正規表現とは、いくつかの文字列のパターンを、一つの文字列で表現する方式である。</t>
+    <rPh sb="0" eb="2">
+      <t>セイキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>モジレツ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ホウシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データ構造</t>
+  </si>
+  <si>
+    <t>データ構造</t>
+    <rPh sb="3" eb="5">
+      <t>コウゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q27</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q29</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A, C, K, S, Tの順に文字が入力される。スタックを利用して、S, T, A, C, Kという順に文字を出力するために、最小限必要となるスタックは何個か。ここで、どのスタックにおいてもポップ操作が実行されたときには必ず文字を出力する。また、スタック間の文字の移動は行わない。</t>
+    <rPh sb="14" eb="15">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="64" eb="67">
+      <t>サイショウゲン</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ナンコ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="111" eb="112">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="130" eb="132">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタックとは、最後に追加したデータから順に取り出されていく、後入れ先出し(LIFO : Last In First Out)方式のデータ構造。データを追加する操作をpushと呼び、データを取り出す操作をpopと呼ぶ。
+面倒なので最低限の説明をする。最低だ。
+スタックが2個の場合、
+(),()
+まずはAを入れるが、次にCを考える。AをCより先に取り出したいので、Aとは別のスタックに入れる必要がある。
+(A), (C)
+次にKをについてだが、KはAとCのどちらよりも後に取り出したいので、どちらのスタックにも入れることができない。したがって、スタックが2個では足りない。
+真に驚くべきことに、スタックが3個あれば足りる。しかし、ここに書くには余白が狭すぎる。</t>
+    <rPh sb="7" eb="9">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>アトイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>サキダ</t>
+    </rPh>
+    <rPh sb="62" eb="64">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="96" eb="97">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="105" eb="106">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>メンドウ</t>
+    </rPh>
+    <rPh sb="114" eb="117">
+      <t>サイテイゲン</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>サイテイ</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="157" eb="158">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="161" eb="162">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="170" eb="171">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="172" eb="173">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="174" eb="175">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="191" eb="192">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="194" eb="196">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="210" eb="211">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="233" eb="234">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="235" eb="236">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="237" eb="238">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="254" eb="255">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="277" eb="278">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="280" eb="281">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="286" eb="287">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="288" eb="289">
+      <t>オドロ</t>
+    </rPh>
+    <rPh sb="302" eb="303">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="306" eb="307">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="317" eb="318">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="321" eb="323">
+      <t>ヨハク</t>
+    </rPh>
+    <rPh sb="324" eb="325">
+      <t>セマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q21</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Q22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>待ち行列に対する操作を、次の通りに定義する。
+ENQn : 待ち行列にデータを挿入する。
+DEQ : 待ち行列からデータを取り出す。
+空の待ち行列に対し、ENQ1, ENQ2, ENQ3, DEQ, ENQ4, ENQ5, DEQ, ENQ6, DEQ, DEQの操作を行った。次にDEQ操作を行ったとき、取り出されるデータはどれか。</t>
+    <rPh sb="0" eb="1">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トオ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ソウニュウ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="61" eb="62">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>カラ</t>
+    </rPh>
+    <rPh sb="69" eb="70">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="132" eb="134">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="135" eb="136">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="139" eb="140">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="147" eb="148">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="155" eb="156">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>待ち行列は、先に入ったものから順に先に取り出されていく、先入れ先出し(FIFO : First In First Out)方式のデータ構造である。本問におけるENQはenqueueを、DEQはdeququeを表す。
+()の中身を待ち行列だとみなし、</t>
+    <rPh sb="0" eb="1">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギョウレツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サキイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サキダ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>ホウシキ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>コウゾウ</t>
+    </rPh>
+    <rPh sb="73" eb="74">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="74" eb="75">
+      <t>モン</t>
+    </rPh>
+    <rPh sb="104" eb="105">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ナカミ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>ギョウレツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -256,11 +3292,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -541,12 +3582,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="13.8984375" customWidth="1"/>
     <col min="2" max="2" width="14.59765625" customWidth="1"/>
-    <col min="3" max="3" width="61.19921875" customWidth="1"/>
+    <col min="3" max="3" width="69.09765625" customWidth="1"/>
     <col min="4" max="4" width="74.296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -564,7 +3605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="49.8" customHeight="1">
+    <row r="2" spans="1:4" ht="34.200000000000003" customHeight="1">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -578,7 +3619,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="61.2" customHeight="1">
+    <row r="3" spans="1:4" ht="37.200000000000003" customHeight="1">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -586,13 +3627,13 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="67.8" customHeight="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="32.4" customHeight="1">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -606,7 +3647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.8" customHeight="1">
+    <row r="5" spans="1:4" ht="36" customHeight="1">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -620,7 +3661,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="52.2" customHeight="1">
+    <row r="6" spans="1:4" ht="35.4" customHeight="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -634,7 +3675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="69" customHeight="1">
+    <row r="7" spans="1:4" ht="36" customHeight="1">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -648,7 +3689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="65.400000000000006" customHeight="1">
+    <row r="8" spans="1:4" ht="36" customHeight="1">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -662,7 +3703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="56.4" customHeight="1">
+    <row r="9" spans="1:4" ht="39" customHeight="1">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -676,7 +3717,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="90">
+    <row r="10" spans="1:4" ht="34.799999999999997" customHeight="1">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -690,7 +3731,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="126">
+    <row r="11" spans="1:4" ht="39" customHeight="1">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -704,18 +3745,3003 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="162">
+    <row r="12" spans="1:4" ht="35.4" customHeight="1">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A16" t="s">
+        <v>221</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A19" t="s">
+        <v>224</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A22" t="s">
+        <v>227</v>
+      </c>
+      <c r="B22" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B23" t="s">
+        <v>277</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A25" t="s">
+        <v>279</v>
+      </c>
+      <c r="B25" t="s">
+        <v>277</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A26" t="s">
+        <v>280</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A28" t="s">
+        <v>282</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A29" t="s">
+        <v>283</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A30" t="s">
+        <v>284</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C32" s="2"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C33" s="2"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C34" s="2"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C36" s="2"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C37" s="2"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C38" s="2"/>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C39" s="2"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C40" s="2"/>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C41" s="2"/>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C42" s="2"/>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C43" s="2"/>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C44" s="2"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C45" s="2"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:4" ht="35.4" customHeight="1">
+      <c r="C46" s="2"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="48" spans="1:4" ht="34.200000000000003" customHeight="1">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="39" customHeight="1">
+      <c r="A49" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="36.6" customHeight="1">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="43.2" customHeight="1">
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="39.6" customHeight="1">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+      <c r="C52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="35.4" customHeight="1">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" t="s">
+        <v>63</v>
+      </c>
+      <c r="D55" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="30" customHeight="1">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+      <c r="B62" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" t="s">
+        <v>84</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="43.2" customHeight="1">
+      <c r="A63" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="46.2" customHeight="1">
+      <c r="A65" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>92</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="36">
+      <c r="A66" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>95</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="45" customHeight="1">
+      <c r="A67" t="s">
+        <v>97</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>100</v>
+      </c>
+      <c r="B68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" t="s">
+        <v>101</v>
+      </c>
+      <c r="D68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588A9827-E233-457F-9105-14E4A75C22B2}">
+  <dimension ref="A1:D206"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="5.19921875" customWidth="1"/>
+    <col min="3" max="3" width="57.09765625" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>200</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>250</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>313</v>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0.05</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>0.125</v>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>0.375</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33">
+        <v>0.5</v>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0.12</v>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40">
+        <v>0.75</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>0.84</v>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>132</v>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>208</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>50</v>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>500</v>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49">
+        <v>5000</v>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>213</v>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>212</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>212</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>215</v>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>232</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>232</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>234</v>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>232</v>
+      </c>
+      <c r="B56">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>235</v>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>239</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>241</v>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>239</v>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>242</v>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>239</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>244</v>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>247</v>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>248</v>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>249</v>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>250</v>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>253</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>255</v>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>253</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>256</v>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>253</v>
+      </c>
+      <c r="B68">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>257</v>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>253</v>
+      </c>
+      <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>254</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>261</v>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>262</v>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>254</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>263</v>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>254</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>267</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>268</v>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>267</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>269</v>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>270</v>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>267</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>236</v>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>456789</v>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>271</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>272</v>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>271</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>273</v>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>271</v>
+      </c>
+      <c r="B81">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>274</v>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>288</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>288</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>288</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>288</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>289</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>289</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>289</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>289</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>39</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>125</v>
+      </c>
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>39</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124">
+        <v>250</v>
+      </c>
+      <c r="D124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>39</v>
+      </c>
+      <c r="B125">
+        <v>3</v>
+      </c>
+      <c r="C125">
+        <v>80000</v>
+      </c>
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126">
+        <v>4</v>
+      </c>
+      <c r="C126">
+        <v>125000</v>
+      </c>
+      <c r="D126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>43</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>135</v>
+      </c>
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>43</v>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>136</v>
+      </c>
+      <c r="D128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B129">
+        <v>3</v>
+      </c>
+      <c r="C129" t="s">
+        <v>137</v>
+      </c>
+      <c r="D129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>138</v>
+      </c>
+      <c r="D130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>46</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131" t="s">
+        <v>139</v>
+      </c>
+      <c r="D131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>46</v>
+      </c>
+      <c r="B132">
+        <v>2</v>
+      </c>
+      <c r="C132" t="s">
+        <v>140</v>
+      </c>
+      <c r="D132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>46</v>
+      </c>
+      <c r="B133">
+        <v>3</v>
+      </c>
+      <c r="C133" t="s">
+        <v>141</v>
+      </c>
+      <c r="D133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>46</v>
+      </c>
+      <c r="B134">
+        <v>4</v>
+      </c>
+      <c r="C134" t="s">
+        <v>142</v>
+      </c>
+      <c r="D134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>49</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>7</v>
+      </c>
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>49</v>
+      </c>
+      <c r="B136">
+        <v>2</v>
+      </c>
+      <c r="C136">
+        <v>8</v>
+      </c>
+      <c r="D136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>49</v>
+      </c>
+      <c r="B137">
+        <v>3</v>
+      </c>
+      <c r="C137">
+        <v>9</v>
+      </c>
+      <c r="D137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>49</v>
+      </c>
+      <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138">
+        <v>10</v>
+      </c>
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>53</v>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139" t="s">
+        <v>143</v>
+      </c>
+      <c r="D139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>53</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>144</v>
+      </c>
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>53</v>
+      </c>
+      <c r="B141">
+        <v>3</v>
+      </c>
+      <c r="C141" t="s">
+        <v>145</v>
+      </c>
+      <c r="D141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>53</v>
+      </c>
+      <c r="B142">
+        <v>4</v>
+      </c>
+      <c r="C142" t="s">
+        <v>146</v>
+      </c>
+      <c r="D142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>56</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>147</v>
+      </c>
+      <c r="D143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>56</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>148</v>
+      </c>
+      <c r="D144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
+        <v>56</v>
+      </c>
+      <c r="B145">
+        <v>3</v>
+      </c>
+      <c r="C145" t="s">
+        <v>149</v>
+      </c>
+      <c r="D145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>56</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146" t="s">
+        <v>150</v>
+      </c>
+      <c r="D146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>59</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147" t="s">
+        <v>151</v>
+      </c>
+      <c r="D147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>59</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" s="4">
+        <v>46042</v>
+      </c>
+      <c r="D148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>59</v>
+      </c>
+      <c r="B149">
+        <v>3</v>
+      </c>
+      <c r="C149" s="4">
+        <v>46032</v>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
+        <v>59</v>
+      </c>
+      <c r="B150">
+        <v>4</v>
+      </c>
+      <c r="C150" s="4">
+        <v>46027</v>
+      </c>
+      <c r="D150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
+        <v>62</v>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
+        <v>152</v>
+      </c>
+      <c r="D151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>62</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>153</v>
+      </c>
+      <c r="D152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>62</v>
+      </c>
+      <c r="B153">
+        <v>3</v>
+      </c>
+      <c r="C153" t="s">
+        <v>154</v>
+      </c>
+      <c r="D153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>62</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154" t="s">
+        <v>155</v>
+      </c>
+      <c r="D154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>65</v>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155" t="s">
+        <v>156</v>
+      </c>
+      <c r="D155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>65</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156" t="s">
+        <v>157</v>
+      </c>
+      <c r="D156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>65</v>
+      </c>
+      <c r="B157">
+        <v>3</v>
+      </c>
+      <c r="C157" t="s">
+        <v>158</v>
+      </c>
+      <c r="D157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>65</v>
+      </c>
+      <c r="B158">
+        <v>4</v>
+      </c>
+      <c r="C158" t="s">
+        <v>159</v>
+      </c>
+      <c r="D158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>68</v>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159" t="s">
+        <v>160</v>
+      </c>
+      <c r="D159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>68</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160" t="s">
+        <v>161</v>
+      </c>
+      <c r="D160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>68</v>
+      </c>
+      <c r="B161">
+        <v>3</v>
+      </c>
+      <c r="C161" t="s">
+        <v>162</v>
+      </c>
+      <c r="D161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>68</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162" t="s">
+        <v>163</v>
+      </c>
+      <c r="D162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>70</v>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>164</v>
+      </c>
+      <c r="D163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>70</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
+        <v>165</v>
+      </c>
+      <c r="D164" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>70</v>
+      </c>
+      <c r="B165">
+        <v>3</v>
+      </c>
+      <c r="C165" t="s">
+        <v>166</v>
+      </c>
+      <c r="D165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>70</v>
+      </c>
+      <c r="B166">
+        <v>4</v>
+      </c>
+      <c r="C166" t="s">
+        <v>167</v>
+      </c>
+      <c r="D166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>74</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167" t="s">
+        <v>168</v>
+      </c>
+      <c r="D167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>74</v>
+      </c>
+      <c r="B168">
+        <v>2</v>
+      </c>
+      <c r="C168" t="s">
+        <v>169</v>
+      </c>
+      <c r="D168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>74</v>
+      </c>
+      <c r="B169">
+        <v>3</v>
+      </c>
+      <c r="C169" t="s">
+        <v>170</v>
+      </c>
+      <c r="D169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>74</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170" t="s">
+        <v>171</v>
+      </c>
+      <c r="D170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>77</v>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
+        <v>172</v>
+      </c>
+      <c r="D171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>77</v>
+      </c>
+      <c r="B172">
+        <v>2</v>
+      </c>
+      <c r="C172" t="s">
+        <v>173</v>
+      </c>
+      <c r="D172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>77</v>
+      </c>
+      <c r="B173">
+        <v>3</v>
+      </c>
+      <c r="C173" t="s">
+        <v>174</v>
+      </c>
+      <c r="D173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>77</v>
+      </c>
+      <c r="B174">
+        <v>4</v>
+      </c>
+      <c r="C174" t="s">
+        <v>175</v>
+      </c>
+      <c r="D174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>80</v>
+      </c>
+      <c r="B175">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>176</v>
+      </c>
+      <c r="D175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" t="s">
+        <v>80</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+      <c r="C176" t="s">
+        <v>177</v>
+      </c>
+      <c r="D176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" t="s">
+        <v>80</v>
+      </c>
+      <c r="B177">
+        <v>3</v>
+      </c>
+      <c r="C177" t="s">
+        <v>178</v>
+      </c>
+      <c r="D177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" t="s">
+        <v>80</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178" t="s">
+        <v>179</v>
+      </c>
+      <c r="D178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" t="s">
+        <v>83</v>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179" t="s">
+        <v>180</v>
+      </c>
+      <c r="D179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" t="s">
+        <v>83</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+      <c r="C180" t="s">
+        <v>181</v>
+      </c>
+      <c r="D180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" t="s">
+        <v>83</v>
+      </c>
+      <c r="B181">
+        <v>3</v>
+      </c>
+      <c r="C181" t="s">
+        <v>182</v>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" t="s">
+        <v>83</v>
+      </c>
+      <c r="B182">
+        <v>4</v>
+      </c>
+      <c r="C182" t="s">
+        <v>183</v>
+      </c>
+      <c r="D182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" t="s">
+        <v>86</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183" t="s">
+        <v>184</v>
+      </c>
+      <c r="D183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
+      <c r="A184" t="s">
+        <v>86</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184" t="s">
+        <v>185</v>
+      </c>
+      <c r="D184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" t="s">
+        <v>86</v>
+      </c>
+      <c r="B185">
+        <v>3</v>
+      </c>
+      <c r="C185" t="s">
+        <v>186</v>
+      </c>
+      <c r="D185" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" t="s">
+        <v>86</v>
+      </c>
+      <c r="B186">
+        <v>4</v>
+      </c>
+      <c r="C186" t="s">
+        <v>187</v>
+      </c>
+      <c r="D186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" t="s">
+        <v>89</v>
+      </c>
+      <c r="B187">
+        <v>1</v>
+      </c>
+      <c r="C187">
+        <v>1.011E-3</v>
+      </c>
+      <c r="D187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" t="s">
+        <v>89</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188">
+        <v>1.101E-3</v>
+      </c>
+      <c r="D188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" t="s">
+        <v>89</v>
+      </c>
+      <c r="B189">
+        <v>3</v>
+      </c>
+      <c r="C189">
+        <v>1.1100000000000001E-3</v>
+      </c>
+      <c r="D189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
+      <c r="A190" t="s">
+        <v>89</v>
+      </c>
+      <c r="B190">
+        <v>4</v>
+      </c>
+      <c r="C190">
+        <v>1.11E-2</v>
+      </c>
+      <c r="D190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" t="s">
+        <v>91</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>188</v>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
+      <c r="A192" t="s">
+        <v>91</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192" t="s">
+        <v>189</v>
+      </c>
+      <c r="D192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
+      <c r="A193" t="s">
+        <v>91</v>
+      </c>
+      <c r="B193">
+        <v>3</v>
+      </c>
+      <c r="C193" t="s">
+        <v>190</v>
+      </c>
+      <c r="D193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
+      <c r="A194" t="s">
+        <v>91</v>
+      </c>
+      <c r="B194">
+        <v>4</v>
+      </c>
+      <c r="C194" t="s">
+        <v>191</v>
+      </c>
+      <c r="D194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
+      <c r="A195" t="s">
+        <v>94</v>
+      </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>192</v>
+      </c>
+      <c r="D195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
+      <c r="A196" t="s">
+        <v>94</v>
+      </c>
+      <c r="B196">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>193</v>
+      </c>
+      <c r="D196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
+      <c r="A197" t="s">
+        <v>94</v>
+      </c>
+      <c r="B197">
+        <v>3</v>
+      </c>
+      <c r="C197" t="s">
+        <v>194</v>
+      </c>
+      <c r="D197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
+      <c r="A198" t="s">
+        <v>94</v>
+      </c>
+      <c r="B198">
+        <v>4</v>
+      </c>
+      <c r="C198" t="s">
+        <v>195</v>
+      </c>
+      <c r="D198" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
+      <c r="A199" t="s">
+        <v>97</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>196</v>
+      </c>
+      <c r="D199" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
+      <c r="A200" t="s">
+        <v>97</v>
+      </c>
+      <c r="B200">
+        <v>2</v>
+      </c>
+      <c r="C200" t="s">
+        <v>197</v>
+      </c>
+      <c r="D200" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
+      <c r="A201" t="s">
+        <v>97</v>
+      </c>
+      <c r="B201">
+        <v>3</v>
+      </c>
+      <c r="C201" t="s">
+        <v>198</v>
+      </c>
+      <c r="D201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
+      <c r="A202" t="s">
+        <v>97</v>
+      </c>
+      <c r="B202">
+        <v>4</v>
+      </c>
+      <c r="C202" t="s">
+        <v>199</v>
+      </c>
+      <c r="D202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
+      <c r="A203" t="s">
+        <v>100</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203" t="s">
+        <v>200</v>
+      </c>
+      <c r="D203" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
+      <c r="A204" t="s">
+        <v>100</v>
+      </c>
+      <c r="B204">
+        <v>2</v>
+      </c>
+      <c r="C204" t="s">
+        <v>201</v>
+      </c>
+      <c r="D204" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
+      <c r="A205" t="s">
+        <v>100</v>
+      </c>
+      <c r="B205">
+        <v>3</v>
+      </c>
+      <c r="C205" t="s">
+        <v>202</v>
+      </c>
+      <c r="D205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
+      <c r="A206" t="s">
+        <v>100</v>
+      </c>
+      <c r="B206">
+        <v>4</v>
+      </c>
+      <c r="C206" t="s">
+        <v>203</v>
+      </c>
+      <c r="D206" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
